--- a/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>Four 3-ring paella burners with legs (an XL 3-ring burner with tripod and regulator for pans up to 36 in (90 cm) runs about 549: Kit estimate from store prices), a rolling stand (about 399 for a 2-ring one) and wind guards. Get quotes before you buy.</t>
+          <t>Four 3-ring paella burners with legs (the XL 3-ring burner with tripod and regulator for pans up to 36 in (90 cm) runs about 549; burners for the 26-32 in pans cost less: Kit estimate from store prices), a rolling stand (about 399 for a 2-ring one) and wind guards. Get quotes before you buy.</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="J7" s="28" t="inlineStr">
         <is>
-          <t>Servers and buffet attendants hired per event and paid hourly as W-2 employees, about one team member per 25 guests (miamigrillcatering.com). Their FTE is a fraction because they only work event hours. Treating them as 1099 contractors is a misclassification risk (FLSA; California AB5). Paid at or above the pay floor in proportion to FTE. The voluntary gratuity is theirs.</t>
+          <t>Servers and buffet attendants hired per event and paid hourly as W-2 employees, about one team member per 25 guests (miamigrillcatering.com). Their FTE is a fraction because they only work event hours. Treating them as 1099 contractors is a misclassification risk (FLSA; California AB5). Paid at or above the pay floor in proportion to FTE. The voluntary gratuity is theirs. One of them acts as event captain on the day.</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="J19" s="35" t="inlineStr">
         <is>
-          <t>Average number of people working each event: 1 on a drop-off, 2 at a backyard paella party, 3 at a company event, 4.5 at a wedding and 4 at a premium seafood event (Kit estimate). Weighted by the example mix in the Word plan, that averages about 2.5. Raise it for bigger events: the staffing sizes itself.</t>
+          <t>Average number of people working each event: 1 on a drop-off, 2 at a backyard paella party, 3 at a company event, 4.5 at a wedding and 4 at a premium seafood event (Kit estimate, about one team member per 25 guests). A full-service wedding with a tapas hour, like the calculator's example (2 paella chefs, a helper and 5 servers), takes 8: across 18 weddings that adds about 570 hours, and coverage stays above 100%. Weighted by the example mix in the Word plan, the average is about 2.5. Raise it if you staff like the calculator: the staffing sizes itself.</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3-3.5 oz (80-100 g) uncooked</t>
+          <t>3-3.5 oz (85-100 g) uncooked</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
@@ -2113,7 +2113,7 @@
         <v>0.02899990782975031</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (paella burners and stands, paella pans, used cargo van, van upfit and the fire / propane setup inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (paella burners and stands, paella pans, used cargo van, van upfit and the fire / propane setup inspection), not of the whole block: the other items are left out. No lender funds a build-out without a "&amp;"cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (paella burners and stands, paella pans, used cargo van, van upfit and the fire / propane setup inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>5734.285714285714</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital "&amp;"reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to 52186 of the 88966 total investment.</v>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
         <v>0.03</v>
       </c>
       <c r="F18" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra seafood, ice, lemons, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van fuel, maintenance and registration are in row 27; propane is in row 15)","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra seafood, ice, lemons, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van fuel, maintenance and registration are in row 27; "&amp;"propane is in row 15)","")</f>
         <v>At 3% of sales: a cushion for unbudgeted event costs (extra seafood, ice, lemons, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van fuel, maintenance and registration are in row 27; propane is in row 15)</v>
       </c>
       <c r="G18" s="68">
@@ -7344,7 +7344,7 @@
         <v>-120862.18031707316</v>
       </c>
       <c r="O11" s="28" t="str">
-        <f>IFERROR("Paella ingredient and add-on purchases, disposables and cooking fuel, fees and contingencies, each at ITS tax rate (column G of the P&amp;L; 0 in the US, where the sales tax you pay is part of the cost) and with the supplier payment days from ""0. Assumptions""."&amp;IF('0. Assumptions'!$B$59=0,""," With "&amp;TEXT('0. Assumptions'!$B$59,"0")&amp;" payment days, the last purchases of the year are paid next year: the ""Year"" column of this row holds "&amp;TEXT(MAX(0,12-ROUNDUP('0. Assumptions'!$B$59/30,0)),"0")&amp;" months of purchases, not the year's cost."),"")</f>
+        <f>IFERROR("Paella ingredient and add-on purchases, disposables and cooking fuel, fees and contingencies, each at ITS tax rate (column G of the P&amp;L; 0 in the US, where the sales tax you pay is part of the cost) and with the supplier payment days from "&amp;"""0. Assumptions""."&amp;IF('0. Assumptions'!$B$59=0,""," With "&amp;TEXT('0. Assumptions'!$B$59,"0")&amp;" payment days, the last purchases of the year are paid next year: the ""Year"" column of this row holds "&amp;TEXT(MAX(0,12-ROUNDUP('0. Assumptions'!$B$59/30,0)),"0")&amp;" months of purchases, not the year's cost."),"")</f>
         <v>Paella ingredient and add-on purchases, disposables and cooking fuel, fees and contingencies, each at ITS tax rate (column G of the P&amp;L; 0 in the US, where the sales tax you pay is part of the cost) and with the supplier payment days from "0. Assumptions". With 7 payment days, the last purchases of the year are paid next year: the "Year" column of this row holds 11 months of purchases, not the year's cost.</v>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
@@ -2113,7 +2113,7 @@
         <v>0.02899990782975031</v>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (paella burners and stands, paella pans, used cargo van, van upfit and the fire / propane setup inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (paella burners and stands, paella pans, used cargo van, van upfit and the fire / propane setup inspection), not of the whole block: the other items are left out. No lender funds a build-out without a "&amp;"cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (paella burners and stands, paella pans, used cargo van, van upfit and the fire / propane setup inspection), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E23" s="28" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>5734.285714285714</v>
       </c>
       <c r="D33" s="37" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital "&amp;"reserve. They add up to "&amp;TEXT(B26-B31-B32,"#,##0")&amp;" of the "&amp;TEXT(B26,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, first-year permits and certifications, opening inventory, website, photos and launch, the commissary deposit, pre-opening commissary rent and the working capital reserve. They add up to 52186 of the 88966 total investment.</v>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
         <v>0.03</v>
       </c>
       <c r="F18" s="28" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra seafood, ice, lemons, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van fuel, maintenance and registration are in row 27; propane is in row 15)","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$28,"0%")&amp;" of sales: a cushion for unbudgeted event costs (extra seafood, ice, lemons, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van fuel, maintenance and registration are in row 27; "&amp;"propane is in row 15)","")</f>
         <v>At 3% of sales: a cushion for unbudgeted event costs (extra seafood, ice, lemons, venue parking). It is a VARIABLE cost: it moves with the number of events, so it cannot sit in fixed costs (van fuel, maintenance and registration are in row 27; propane is in row 15)</v>
       </c>
       <c r="G18" s="68">
@@ -7344,7 +7344,7 @@
         <v>-120862.18031707316</v>
       </c>
       <c r="O11" s="28" t="str">
-        <f>IFERROR("Paella ingredient and add-on purchases, disposables and cooking fuel, fees and contingencies, each at ITS tax rate (column G of the P&amp;L; 0 in the US, where the sales tax you pay is part of the cost) and with the supplier payment days from ""0. Assumptions""."&amp;IF('0. Assumptions'!$B$59=0,""," With "&amp;TEXT('0. Assumptions'!$B$59,"0")&amp;" payment days, the last purchases of the year are paid next year: the ""Year"" column of this row holds "&amp;TEXT(MAX(0,12-ROUNDUP('0. Assumptions'!$B$59/30,0)),"0")&amp;" months of purchases, not the year's cost."),"")</f>
+        <f>IFERROR("Paella ingredient and add-on purchases, disposables and cooking fuel, fees and contingencies, each at ITS tax rate (column G of the P&amp;L; 0 in the US, where the sales tax you pay is part of the cost) and with the supplier payment days from "&amp;"""0. Assumptions""."&amp;IF('0. Assumptions'!$B$59=0,""," With "&amp;TEXT('0. Assumptions'!$B$59,"0")&amp;" payment days, the last purchases of the year are paid next year: the ""Year"" column of this row holds "&amp;TEXT(MAX(0,12-ROUNDUP('0. Assumptions'!$B$59/30,0)),"0")&amp;" months of purchases, not the year's cost."),"")</f>
         <v>Paella ingredient and add-on purchases, disposables and cooking fuel, fees and contingencies, each at ITS tax rate (column G of the P&amp;L; 0 in the US, where the sales tax you pay is part of the cost) and with the supplier payment days from "0. Assumptions". With 7 payment days, the last purchases of the year are paid next year: the "Year" column of this row holds 11 months of purchases, not the year's cost.</v>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>

--- a/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
+++ b/astro-site/public/dl/paella-catering-business-plan/paella-catering-financial-projections.xlsx
@@ -8236,7 +8236,7 @@
       <c r="N33" s="28" t="n"/>
       <c r="O33" s="28" t="n"/>
     </row>
-    <row r="34" ht="134.75" customHeight="1">
+    <row r="34" ht="149.5" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
